--- a/Leader NHÓM 6/báo_Cáo_Tuần_t2_2026.xlsx
+++ b/Leader NHÓM 6/báo_Cáo_Tuần_t2_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\RIKKEI\Leader NHÓM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4379FBAD-D963-46E3-A428-225D4D288792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C239497D-CC54-4312-B0E8-232D1AA3DA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="39">
   <si>
     <t>BÁO CÁO HOẠT ĐỘNG TUẦN CỦA NHÓM</t>
   </si>
@@ -137,28 +137,22 @@
     <t>Nguyễn Thiện Thuật</t>
   </si>
   <si>
-    <t>Chủ động làm bài tập , hợp tác tốt, nghỉ học 1 hôm ( Có phép )</t>
-  </si>
-  <si>
-    <t>Chủ động làm bài tập , hợp tác tốt, có đón góp xây dựng bài. Nghỉ 1 hôm ( Có phép )</t>
-  </si>
-  <si>
     <t>Không Hoàn Thành</t>
   </si>
   <si>
     <t>Nghỉ học vô tội vạ không báo lên portal</t>
   </si>
   <si>
-    <t>Làm bài tập đầy đủ, có một hôm đi học muộn, có đóng góp tham gia xây dựng bài</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chủ động làm bài tập , hợp tác khá, có đi học muộn </t>
-  </si>
-  <si>
-    <t>nghỉ học cả tuần tháng</t>
-  </si>
-  <si>
-    <t>Đề xuất: Kick ra khỏi nhóm ạ</t>
+    <t xml:space="preserve">Chủ động làm bài tập , hợp tác tốt, có đón góp xây dựng bài. </t>
+  </si>
+  <si>
+    <t>Làm bài tập đầy đủ, có đóng góp tham gia xây dựng bài</t>
+  </si>
+  <si>
+    <t>Đã loại</t>
+  </si>
+  <si>
+    <t>Dã loại</t>
   </si>
 </sst>
 </file>
@@ -617,12 +611,14 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="6">
-        <v>46236</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
@@ -712,7 +708,7 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -735,7 +731,7 @@
         <v>28</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>25</v>
@@ -773,9 +769,7 @@
       <c r="G8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
         <v>25</v>
       </c>
@@ -804,22 +798,22 @@
         <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -854,7 +848,7 @@
         <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>25</v>
@@ -893,7 +887,7 @@
         <v>28</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>25</v>
